--- a/data/trans_dic/IP04D$aparatos-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,55; 77,96</t>
+          <t>62,48; 77,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,25; 73,07</t>
+          <t>53,53; 73,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,68; 79,13</t>
+          <t>42,54; 78,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,11; 79,11</t>
+          <t>63,12; 79,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,67; 75,63</t>
+          <t>56,29; 75,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,04; 76,67</t>
+          <t>54,68; 77,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,61; 76,74</t>
+          <t>65,42; 76,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57,23; 71,0</t>
+          <t>56,86; 71,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53,31; 73,81</t>
+          <t>51,94; 73,78</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,59; 71,67</t>
+          <t>64,78; 71,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,99; 58,26</t>
+          <t>50,75; 58,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,49; 74,87</t>
+          <t>64,03; 74,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,72; 67,81</t>
+          <t>60,76; 68,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,21; 58,87</t>
+          <t>51,02; 58,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,39; 67,58</t>
+          <t>57,71; 68,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,92; 68,73</t>
+          <t>63,8; 68,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,83; 56,9</t>
+          <t>52,1; 57,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62,25; 69,35</t>
+          <t>62,5; 69,48</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,94; 56,53</t>
+          <t>43,28; 56,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,55; 47,37</t>
+          <t>34,41; 46,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,14; 50,36</t>
+          <t>36,74; 50,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,15; 55,7</t>
+          <t>42,77; 55,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,79; 48,61</t>
+          <t>36,28; 48,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,57; 48,27</t>
+          <t>35,43; 47,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,31; 54,52</t>
+          <t>45,2; 54,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37,71; 45,94</t>
+          <t>37,73; 46,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,35; 48,02</t>
+          <t>38,05; 47,23</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,57; 67,45</t>
+          <t>61,42; 67,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,7; 54,71</t>
+          <t>48,77; 54,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,52; 67,49</t>
+          <t>58,8; 67,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59,21; 64,77</t>
+          <t>59,07; 64,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,71; 55,52</t>
+          <t>49,67; 55,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,48; 62,35</t>
+          <t>54,44; 62,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,04; 65,23</t>
+          <t>60,97; 65,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,15; 54,4</t>
+          <t>50,06; 54,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57,47; 63,48</t>
+          <t>57,56; 63,69</t>
         </is>
       </c>
     </row>
@@ -1069,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>65219</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>37144</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35226</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>61789</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>45147</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>41256</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>127008</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>82291</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>76482</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>57708; 71965</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>31450; 43115</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23259; 42661</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>54401; 68605</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>38619; 51705</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>33903; 48103</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>116813; 136485</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>72416; 91691</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>60610; 86083</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>307175</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>255837</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>315522</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>317955</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>266209</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>328236</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>625131</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>522045</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>643758</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>290947; 323111</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>238913; 273655</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>294884; 344960</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>299626; 336343</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>247999; 284652</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>297744; 351486</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>601147; 648415</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>498495; 548321</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>610282; 678432</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>83554</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69358</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65159</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>84917</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79145</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76197</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>168471</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>148503</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>141355</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>72201; 94493</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>58715; 80150</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>54584; 74924</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73667; 95845</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>67224; 90230</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>64624; 87476</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>153254; 183288</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>134309; 164879</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>125939; 156301</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>455948</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>362339</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>415906</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>464662</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>390501</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>445689</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>920609</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>752840</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>861595</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>435016; 476483</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>341465; 382945</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>390256; 448835</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>443984; 486528</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>367598; 413510</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>413919; 476641</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>890115; 950466</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>720906; 781491</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>819712; 907012</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$aparatos-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,48; 77,91</t>
+          <t>62,39; 77,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,53; 73,39</t>
+          <t>53,38; 73,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,54; 78,02</t>
+          <t>44,46; 78,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,12; 79,6</t>
+          <t>62,77; 79,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,29; 75,36</t>
+          <t>55,61; 74,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,68; 77,58</t>
+          <t>54,26; 76,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,42; 76,44</t>
+          <t>64,97; 76,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,86; 71,99</t>
+          <t>57,7; 72,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51,94; 73,78</t>
+          <t>54,1; 73,94</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,78; 71,94</t>
+          <t>64,64; 71,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,75; 58,13</t>
+          <t>50,8; 57,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,03; 74,91</t>
+          <t>64,34; 74,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,76; 68,2</t>
+          <t>60,86; 67,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,02; 58,56</t>
+          <t>50,92; 58,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,71; 68,13</t>
+          <t>57,86; 68,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,8; 68,81</t>
+          <t>63,66; 68,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,1; 57,3</t>
+          <t>51,95; 57,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62,5; 69,48</t>
+          <t>62,38; 69,62</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,28; 56,65</t>
+          <t>43,44; 56,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,41; 46,97</t>
+          <t>33,91; 46,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,74; 50,44</t>
+          <t>37,03; 50,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,77; 55,65</t>
+          <t>42,95; 55,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,28; 48,69</t>
+          <t>36,74; 48,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,43; 47,96</t>
+          <t>34,77; 48,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,2; 54,06</t>
+          <t>45,31; 54,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37,73; 46,32</t>
+          <t>37,41; 45,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,05; 47,23</t>
+          <t>37,96; 47,32</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,42; 67,27</t>
+          <t>61,24; 67,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,77; 54,69</t>
+          <t>48,64; 54,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,8; 67,62</t>
+          <t>58,95; 68,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59,07; 64,73</t>
+          <t>58,6; 64,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,67; 55,88</t>
+          <t>49,55; 55,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,44; 62,69</t>
+          <t>54,1; 62,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,97; 65,11</t>
+          <t>61,02; 65,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,06; 54,26</t>
+          <t>50,14; 54,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57,56; 63,69</t>
+          <t>57,71; 63,49</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57708; 71965</t>
+          <t>57630; 71712</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31450; 43115</t>
+          <t>31359; 43327</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23259; 42661</t>
+          <t>24310; 43059</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54401; 68605</t>
+          <t>54104; 68547</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>38619; 51705</t>
+          <t>38154; 50868</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33903; 48103</t>
+          <t>33646; 47675</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>116813; 136485</t>
+          <t>116014; 136578</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>72416; 91691</t>
+          <t>73484; 91723</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60610; 86083</t>
+          <t>63123; 86274</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>290947; 323111</t>
+          <t>290296; 322792</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>238913; 273655</t>
+          <t>239169; 272899</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>294884; 344960</t>
+          <t>296279; 345131</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>299626; 336343</t>
+          <t>300126; 334241</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>247999; 284652</t>
+          <t>247511; 284721</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>297744; 351486</t>
+          <t>298532; 350980</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>601147; 648415</t>
+          <t>599859; 648570</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>498495; 548321</t>
+          <t>497144; 547270</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>610282; 678432</t>
+          <t>609062; 679815</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>72201; 94493</t>
+          <t>72461; 95000</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58715; 80150</t>
+          <t>57872; 80012</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54584; 74924</t>
+          <t>55015; 75246</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73667; 95845</t>
+          <t>73964; 95613</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67224; 90230</t>
+          <t>68082; 90106</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64624; 87476</t>
+          <t>63431; 89135</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>153254; 183288</t>
+          <t>153615; 183829</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>134309; 164879</t>
+          <t>133177; 163315</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>125939; 156301</t>
+          <t>125621; 156603</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>435016; 476483</t>
+          <t>433746; 477138</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>341465; 382945</t>
+          <t>340584; 383439</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>390256; 448835</t>
+          <t>391276; 452561</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>443984; 486528</t>
+          <t>440462; 485270</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>367598; 413510</t>
+          <t>366690; 411755</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>413919; 476641</t>
+          <t>411370; 473302</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>890115; 950466</t>
+          <t>890850; 951220</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>720906; 781491</t>
+          <t>722137; 784270</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>819712; 907012</t>
+          <t>821839; 904194</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$aparatos-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Estudios-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71,69%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>65,8%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>66,97%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>70,61%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>63,22%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>64,42%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71,69%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>65,8%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>69,79%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,39; 77,64</t>
+          <t>63,11; 79,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,38; 73,75</t>
+          <t>55,67; 75,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,46; 78,75</t>
+          <t>54,71; 77,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62,77; 79,53</t>
+          <t>62,55; 77,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,61; 74,14</t>
+          <t>52,25; 73,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,26; 76,89</t>
+          <t>62,02; 82,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,97; 76,49</t>
+          <t>65,61; 76,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>57,7; 72,02</t>
+          <t>57,23; 71,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54,1; 73,94</t>
+          <t>60,31; 76,69</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64,47%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>54,77%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>65,18%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>68,4%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>54,34%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>68,52%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>64,47%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>54,77%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,64; 71,87</t>
+          <t>60,72; 67,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,8; 57,97</t>
+          <t>51,21; 58,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,34; 74,95</t>
+          <t>59,89; 69,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,86; 67,78</t>
+          <t>64,59; 71,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,92; 58,57</t>
+          <t>50,99; 58,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,86; 68,03</t>
+          <t>63,97; 71,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,66; 68,83</t>
+          <t>63,92; 68,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>51,95; 57,19</t>
+          <t>51,83; 56,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62,38; 69,62</t>
+          <t>63,04; 69,05</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>49,31%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42,71%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43,29%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>50,09%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>40,65%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>43,86%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>49,31%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>42,71%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,44; 56,95</t>
+          <t>43,15; 55,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,91; 46,89</t>
+          <t>36,79; 48,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,03; 50,65</t>
+          <t>37,11; 49,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,95; 55,52</t>
+          <t>43,94; 56,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36,74; 48,62</t>
+          <t>34,55; 47,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,77; 48,87</t>
+          <t>37,65; 50,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,31; 54,22</t>
+          <t>45,31; 54,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37,41; 45,88</t>
+          <t>37,71; 45,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,96; 47,32</t>
+          <t>39,66; 48,84</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>61,82%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52,77%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>60,08%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>64,37%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>51,75%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>62,66%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>61,82%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>61,2%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,24; 67,36</t>
+          <t>59,21; 64,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,64; 54,76</t>
+          <t>49,71; 55,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,95; 68,18</t>
+          <t>56,28; 63,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58,6; 64,57</t>
+          <t>61,57; 67,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,55; 55,64</t>
+          <t>48,7; 54,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,1; 62,25</t>
+          <t>59,23; 65,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,02; 65,16</t>
+          <t>61,04; 65,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,14; 54,46</t>
+          <t>50,15; 54,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57,71; 63,49</t>
+          <t>58,88; 63,82</t>
         </is>
       </c>
     </row>
@@ -1099,20 +1099,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>61789</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>45147</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37993</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>65219</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>37144</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35226</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>61789</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>45147</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41256</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>76482</t>
+          <t>72225</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57630; 71712</t>
+          <t>54395; 68184</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31359; 43327</t>
+          <t>38200; 51894</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24310; 43059</t>
+          <t>31039; 43883</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54104; 68547</t>
+          <t>57773; 72014</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>38154; 50868</t>
+          <t>30699; 42926</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33646; 47675</t>
+          <t>28999; 38705</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>116014; 136578</t>
+          <t>117151; 137027</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73484; 91723</t>
+          <t>72892; 90429</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63123; 86274</t>
+          <t>62413; 79365</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>382</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>431</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>434</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>317955</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>266209</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>309658</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>307175</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>255837</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>315522</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>317955</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>266209</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>328236</t>
+          <t>291825</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>643758</t>
+          <t>601483</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>290296; 322792</t>
+          <t>299470; 334425</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>239169; 272899</t>
+          <t>248917; 286166</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>296279; 345131</t>
+          <t>284538; 328397</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>300126; 334241</t>
+          <t>290086; 321873</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>247511; 284721</t>
+          <t>240049; 274297</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>298532; 350980</t>
+          <t>276652; 308780</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>599859; 648570</t>
+          <t>602319; 647640</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>497144; 547270</t>
+          <t>495989; 544452</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>609062; 679815</t>
+          <t>572057; 626645</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>108</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>84917</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>79145</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>72494</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>83554</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>69358</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65159</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>84917</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>79145</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76197</t>
+          <t>66165</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>141355</t>
+          <t>138658</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>72461; 95000</t>
+          <t>74319; 95931</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57872; 80012</t>
+          <t>68167; 90088</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55015; 75246</t>
+          <t>62146; 83597</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73964; 95613</t>
+          <t>73295; 94296</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68082; 90106</t>
+          <t>58951; 80839</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63431; 89135</t>
+          <t>56065; 75710</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>153615; 183829</t>
+          <t>153633; 184853</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>133177; 163315</t>
+          <t>134224; 163519</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>125621; 156603</t>
+          <t>125472; 154510</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>660</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>538</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>589</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>464662</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>390501</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>420145</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>455948</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>362339</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>415906</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>464662</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>390501</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>445689</t>
+          <t>392221</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>861595</t>
+          <t>812366</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>433746; 477138</t>
+          <t>445037; 486782</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>340584; 383439</t>
+          <t>367827; 410849</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>391276; 452561</t>
+          <t>393508; 445390</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>440462; 485270</t>
+          <t>436076; 477724</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>366690; 411755</t>
+          <t>340992; 383063</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>411370; 473302</t>
+          <t>372021; 412344</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>890850; 951220</t>
+          <t>891042; 952337</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>722137; 784270</t>
+          <t>722197; 783510</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>821839; 904194</t>
+          <t>781551; 847185</t>
         </is>
       </c>
     </row>
